--- a/inspection_forms/026_post_session_survey--inspection_forms.xlsx
+++ b/inspection_forms/026_post_session_survey--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,19 +520,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_questions</t>
+          <t>overall_opinion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What do you like about this seminar?</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Tell us about it.</t>
-        </is>
-      </c>
+          <t>What do you think of the seminar?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -547,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>survey_questions</t>
+          <t>most_interesting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What do you dislike about this seminar?</t>
+          <t>What was the most interesting part of the seminar?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -570,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>survey_answers</t>
+          <t>recommend</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -588,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>survey_answers</t>
+          <t>dislike</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How likely are you to take another seminar from this speaker?</t>
+          <t>What did you not like about the seminar?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -611,23 +607,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>session_length</t>
+          <t>next_seminar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Session length</t>
+          <t>Do you plan on taking another seminar from this speaker?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -639,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>session_prophets</t>
+          <t>session_length</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What were the most memorable moments from this seminar?</t>
+          <t>How long should the seminar be?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -662,7 +658,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>session_prophets</t>
+          <t>memorable_moments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -673,7 +669,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -685,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>session_prophets</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What were the most memorable moments from this seminar?</t>
+          <t>Do you have any comments or feedback about this seminar?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>session_prophets</t>
+          <t>registration_process</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What were the most memorable moments from this seminar?</t>
+          <t>How easy was the registration process?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -726,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>session_prophets</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Do you have any other comments or feedback about this seminar?</t>
+          <t>How clear was the communication from the speaker or organizers?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -754,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>session_prophets</t>
+          <t>speaker_engagement</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How likely are you to recommend this seminar?</t>
+          <t>How engaging was the speaker?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,44 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>session_prophets</t>
+          <t>expectations_met</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Do you have any other comments or feedback about this seminar?</t>
+          <t>How well did the seminar meet your expectations?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>session_prophets</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Do you have any other feedback about this seminar?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -826,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -854,102 +827,340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>survey_answers_choices</t>
+          <t>recommend_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>survey_answers_choices</t>
+          <t>recommend_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>survey_answers_choices</t>
+          <t>next_seminar_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>survey_answers_choices</t>
+          <t>next_seminar_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>session_prophets_choices</t>
+          <t>registration_process_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_easy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very easy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>session_prophets_choices</t>
+          <t>registration_process_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_easy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat easy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>registration_process_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>somewhat_difficult</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Somewhat difficult</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>registration_process_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>very_difficult</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Very difficult</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>communication_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>very_clear</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Very clear</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>communication_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>somewhat_clear</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Somewhat clear</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>communication_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>not_very_clear</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Not very clear</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>communication_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>not_clear_at_all</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Not clear at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>speaker_engagement_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>very_engaging</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Very engaging</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>speaker_engagement_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>somewhat_engaging</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Somewhat engaging</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>speaker_engagement_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>somewhat_not_engaging</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Somewhat not engaging</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>speaker_engagement_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>not_engaging_at_all</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Not engaging at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>expectations_met_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>completely_met_expectations</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Completely met expectations</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>expectations_met_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>mostly_met_expectations</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mostly met expectations</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>expectations_met_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>somewhat_met_expectations</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Somewhat met expectations</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>expectations_met_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>not_met_expectations</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Not met expectations</t>
         </is>
       </c>
     </row>
